--- a/Components/U61-VL82C420FC5/Interposer/vl82c420_pinmap.xlsx
+++ b/Components/U61-VL82C420FC5/Interposer/vl82c420_pinmap.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ahmadbyagowi/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ahmadbyagowi/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8666C4CA-85DF-7540-A3F0-F534C9CE217E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{96837D48-DB32-E447-8CAB-4D726E790B24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1980" yWindow="1840" windowWidth="28040" windowHeight="17440" xr2:uid="{CD2BC785-7C7E-B843-93FC-5228FAB3D53E}"/>
+    <workbookView xWindow="10800" yWindow="1940" windowWidth="28040" windowHeight="17440" xr2:uid="{CD2BC785-7C7E-B843-93FC-5228FAB3D53E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="200">
   <si>
     <t>SA16</t>
   </si>
@@ -615,6 +615,27 @@
   </si>
   <si>
     <t>RAM_RAS1</t>
+  </si>
+  <si>
+    <t>Mpriority</t>
+  </si>
+  <si>
+    <t>RTC-SQW</t>
+  </si>
+  <si>
+    <t>RTC-IRQ#</t>
+  </si>
+  <si>
+    <t>MLADS#</t>
+  </si>
+  <si>
+    <t>MLCLK</t>
+  </si>
+  <si>
+    <t>MLRDY#</t>
+  </si>
+  <si>
+    <t>MLLBA#</t>
   </si>
 </sst>
 </file>
@@ -1287,16 +1308,25 @@
       <c r="A59" t="s">
         <v>53</v>
       </c>
+      <c r="B59" t="s">
+        <v>195</v>
+      </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>55</v>
       </c>
+      <c r="B60" t="s">
+        <v>194</v>
+      </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>56</v>
       </c>
+      <c r="B61" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
@@ -1373,20 +1403,32 @@
       <c r="A75" t="s">
         <v>70</v>
       </c>
+      <c r="B75" t="s">
+        <v>199</v>
+      </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>71</v>
       </c>
+      <c r="B76" t="s">
+        <v>197</v>
+      </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>72</v>
       </c>
+      <c r="B77" t="s">
+        <v>198</v>
+      </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>73</v>
+      </c>
+      <c r="B78" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">

--- a/Components/U61-VL82C420FC5/Interposer/vl82c420_pinmap.xlsx
+++ b/Components/U61-VL82C420FC5/Interposer/vl82c420_pinmap.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ahmadbyagowi/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{96837D48-DB32-E447-8CAB-4D726E790B24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{978111F2-F50D-AC46-988A-E3024787E47D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10800" yWindow="1940" windowWidth="28040" windowHeight="17440" xr2:uid="{CD2BC785-7C7E-B843-93FC-5228FAB3D53E}"/>
+    <workbookView xWindow="16220" yWindow="4440" windowWidth="28040" windowHeight="17440" xr2:uid="{CD2BC785-7C7E-B843-93FC-5228FAB3D53E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="193">
   <si>
     <t>SA16</t>
   </si>
@@ -77,27 +77,12 @@
     <t>SBHE#</t>
   </si>
   <si>
-    <t>PNET7</t>
-  </si>
-  <si>
-    <t>PNET1</t>
-  </si>
-  <si>
-    <t>VL_F15</t>
-  </si>
-  <si>
-    <t>VL_F16</t>
-  </si>
-  <si>
     <t>MEMW#</t>
   </si>
   <si>
     <t>MEMR#</t>
   </si>
   <si>
-    <t>BIOS_CE#</t>
-  </si>
-  <si>
     <t>AEN</t>
   </si>
   <si>
@@ -125,12 +110,6 @@
     <t>IOW#</t>
   </si>
   <si>
-    <t>VL_K13</t>
-  </si>
-  <si>
-    <t>VL_K16</t>
-  </si>
-  <si>
     <t>BALE</t>
   </si>
   <si>
@@ -191,27 +170,9 @@
     <t>RESET</t>
   </si>
   <si>
-    <t>U22_CS#</t>
-  </si>
-  <si>
-    <t>TP1</t>
-  </si>
-  <si>
-    <t>VL_N12</t>
-  </si>
-  <si>
     <t>VL_P13</t>
   </si>
   <si>
-    <t>VL_R13</t>
-  </si>
-  <si>
-    <t>VL_T13</t>
-  </si>
-  <si>
-    <t>YMF_VSS</t>
-  </si>
-  <si>
     <t>VL_L11</t>
   </si>
   <si>
@@ -248,18 +209,6 @@
     <t>VL_N10</t>
   </si>
   <si>
-    <t>P9_Bowman</t>
-  </si>
-  <si>
-    <t>R9_Bowman</t>
-  </si>
-  <si>
-    <t>T9_Bowman</t>
-  </si>
-  <si>
-    <t>N9_Bowman</t>
-  </si>
-  <si>
     <t>PullDN1</t>
   </si>
   <si>
@@ -407,9 +356,6 @@
     <t>CPU_EADS#</t>
   </si>
   <si>
-    <t>CPU_A20#</t>
-  </si>
-  <si>
     <t>CPU_RESET</t>
   </si>
   <si>
@@ -431,9 +377,6 @@
     <t>CPU_SMI#</t>
   </si>
   <si>
-    <t>VL_F3</t>
-  </si>
-  <si>
     <t>VL_F5</t>
   </si>
   <si>
@@ -539,15 +482,9 @@
     <t>RAM_WE#</t>
   </si>
   <si>
-    <t>TAM_UCASL#</t>
-  </si>
-  <si>
     <t>RAM_LCASL#</t>
   </si>
   <si>
-    <t>RAM_LCASU</t>
-  </si>
-  <si>
     <t>RAM_A11</t>
   </si>
   <si>
@@ -636,6 +573,48 @@
   </si>
   <si>
     <t>MLLBA#</t>
+  </si>
+  <si>
+    <t>RAM_UCASL#</t>
+  </si>
+  <si>
+    <t>VCC</t>
+  </si>
+  <si>
+    <t>VCC2</t>
+  </si>
+  <si>
+    <t>VSS</t>
+  </si>
+  <si>
+    <t>RAM_LCASU#</t>
+  </si>
+  <si>
+    <t>SUS_STAT#</t>
+  </si>
+  <si>
+    <t>A20GATE</t>
+  </si>
+  <si>
+    <t>ROMCS0#</t>
+  </si>
+  <si>
+    <t>ROMCS1#</t>
+  </si>
+  <si>
+    <t>ISACLK2</t>
+  </si>
+  <si>
+    <t>ISACLK</t>
+  </si>
+  <si>
+    <t>ONCE#</t>
+  </si>
+  <si>
+    <t>MASTER#</t>
+  </si>
+  <si>
+    <t>ROM16/8#</t>
   </si>
 </sst>
 </file>
@@ -1010,10 +989,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05456BA6-FC6A-B84A-9400-3EC3E75B337D}">
   <dimension ref="A1:C208"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="12.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>14</v>
+        <v>180</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
@@ -1083,57 +1065,57 @@
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>181</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>191</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>192</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>186</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.2">
@@ -1143,37 +1125,37 @@
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>29</v>
+        <v>189</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>30</v>
+        <v>188</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.2">
@@ -1183,87 +1165,87 @@
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>13</v>
+        <v>181</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
@@ -1271,179 +1253,158 @@
         <v>9</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>51</v>
+        <v>187</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>53</v>
-      </c>
-      <c r="B59" t="s">
-        <v>195</v>
+        <v>174</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>55</v>
-      </c>
-      <c r="B60" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>56</v>
-      </c>
-      <c r="B61" t="s">
-        <v>193</v>
+        <v>172</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>57</v>
+        <v>182</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="C67" t="s">
-        <v>190</v>
+        <v>169</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="C68" t="s">
-        <v>190</v>
+        <v>169</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>70</v>
-      </c>
-      <c r="B75" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>71</v>
-      </c>
-      <c r="B76" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>72</v>
-      </c>
-      <c r="B77" t="s">
-        <v>198</v>
+        <v>177</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>73</v>
-      </c>
-      <c r="B78" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.2">
@@ -1453,107 +1414,107 @@
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>14</v>
+        <v>180</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.2">
@@ -1561,122 +1522,122 @@
         <v>9</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>14</v>
+        <v>180</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.2">
@@ -1686,137 +1647,137 @@
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>14</v>
+        <v>180</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>123</v>
+        <v>185</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>131</v>
+        <v>184</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>132</v>
+        <v>113</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>134</v>
+        <v>115</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>138</v>
+        <v>119</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>140</v>
+        <v>121</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
-        <v>141</v>
+        <v>122</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>142</v>
+        <v>123</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>143</v>
+        <v>124</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
-        <v>144</v>
+        <v>125</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.2">
@@ -1824,117 +1785,117 @@
         <v>9</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>14</v>
+        <v>180</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
     </row>
     <row r="173" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
-        <v>162</v>
+        <v>143</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
-        <v>163</v>
+        <v>144</v>
       </c>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
     </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
     </row>
     <row r="179" spans="1:1" x14ac:dyDescent="0.2">
@@ -1944,52 +1905,52 @@
     </row>
     <row r="180" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
-        <v>166</v>
+        <v>147</v>
       </c>
     </row>
     <row r="181" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
     </row>
     <row r="182" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
     </row>
     <row r="183" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
-        <v>189</v>
+        <v>168</v>
       </c>
     </row>
     <row r="184" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
     </row>
     <row r="185" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
-        <v>14</v>
+        <v>180</v>
       </c>
     </row>
     <row r="186" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
-        <v>170</v>
+        <v>149</v>
       </c>
     </row>
     <row r="187" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
-        <v>171</v>
+        <v>150</v>
       </c>
     </row>
     <row r="188" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
-        <v>172</v>
+        <v>151</v>
       </c>
     </row>
     <row r="189" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
-        <v>173</v>
+        <v>152</v>
       </c>
     </row>
     <row r="190" spans="1:1" x14ac:dyDescent="0.2">
@@ -1999,87 +1960,87 @@
     </row>
     <row r="191" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
     </row>
     <row r="192" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>176</v>
+        <v>155</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
-        <v>177</v>
+        <v>156</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
-        <v>178</v>
+        <v>157</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
-        <v>14</v>
+        <v>180</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>179</v>
+        <v>158</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
-        <v>180</v>
+        <v>159</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
-        <v>181</v>
+        <v>160</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
-        <v>182</v>
+        <v>161</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
-        <v>183</v>
+        <v>162</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
-        <v>192</v>
+        <v>171</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
-        <v>184</v>
+        <v>163</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
-        <v>186</v>
+        <v>165</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
-        <v>187</v>
+        <v>166</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.2">
@@ -2087,7 +2048,7 @@
         <v>9</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>
